--- a/workbook.xlsx
+++ b/workbook.xlsx
@@ -12,51 +12,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
-    <t>1111</t>
+    <t>CAPEX</t>
   </si>
   <si>
-    <t>sda</t>
+    <t>Hughes Equipment</t>
   </si>
   <si>
-    <t>asa</t>
+    <t>VSAT</t>
   </si>
   <si>
-    <t>qqqqq+qqq</t>
+    <t>1506560-0021+1506561-0021</t>
   </si>
   <si>
-    <t>vv</t>
+    <t>ANTENA 90CM</t>
   </si>
   <si>
-    <t>11</t>
+    <t>90cm Ka-Band Saturated Antenna (Single IFL) 1pk</t>
   </si>
   <si>
-    <t>asda</t>
+    <t>Unit</t>
   </si>
   <si>
-    <t>www</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>da</t>
-  </si>
-  <si>
-    <t>aa</t>
-  </si>
-  <si>
-    <t>ss</t>
-  </si>
-  <si>
-    <t>ad</t>
-  </si>
-  <si>
-    <t>122</t>
+    <t>NRC</t>
   </si>
 </sst>
 </file>
@@ -132,28 +111,28 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="E2" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>12</v>
-      </c>
       <c r="G2" t="s" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
